--- a/ディレクトリマップ_進捗表.xlsx
+++ b/ディレクトリマップ_進捗表.xlsx
@@ -1324,7 +1324,21 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="15">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2697,25 +2711,30 @@
   </sheetData>
   <phoneticPr fontId="4"/>
   <conditionalFormatting sqref="A2">
-    <cfRule type="beginsWith" dxfId="12" priority="3" operator="beginsWith" text="完了">
+    <cfRule type="beginsWith" dxfId="14" priority="4" operator="beginsWith" text="完了">
       <formula>LEFT(A2,2)="完了"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="11" priority="4" operator="beginsWith" text="エラー修正">
+    <cfRule type="beginsWith" dxfId="13" priority="5" operator="beginsWith" text="エラー修正">
       <formula>LEFT(A2,5)="エラー修正"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="10" priority="5" operator="beginsWith" text="着手">
+    <cfRule type="beginsWith" dxfId="12" priority="6" operator="beginsWith" text="着手">
       <formula>LEFT(A2,2)="着手"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:I2 K2:L2 N2:O2">
-    <cfRule type="beginsWith" dxfId="9" priority="1" operator="beginsWith" text="×">
+    <cfRule type="beginsWith" dxfId="11" priority="2" operator="beginsWith" text="×">
       <formula>LEFT(H2,1)="×"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="8" priority="2" operator="beginsWith" text="〇">
+    <cfRule type="beginsWith" dxfId="10" priority="3" operator="beginsWith" text="〇">
       <formula>LEFT(H2,1)="〇"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations disablePrompts="1" count="1">
+  <conditionalFormatting sqref="A4:A45">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"着手"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3:K71 N3:N126 A4 A6:A23 A25:A26 A28 A30:A33">
       <formula1>$W$3:$W$6</formula1>
     </dataValidation>
@@ -3358,21 +3377,21 @@
   </sheetData>
   <phoneticPr fontId="4"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="beginsWith" dxfId="7" priority="5" operator="beginsWith" text="着手">
+    <cfRule type="beginsWith" dxfId="9" priority="5" operator="beginsWith" text="着手">
       <formula>LEFT(B1,2)="着手"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="6" priority="4" operator="beginsWith" text="エラー修正">
+    <cfRule type="beginsWith" dxfId="8" priority="4" operator="beginsWith" text="エラー修正">
       <formula>LEFT(B1,5)="エラー修正"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="5" priority="3" operator="beginsWith" text="完了">
+    <cfRule type="beginsWith" dxfId="7" priority="3" operator="beginsWith" text="完了">
       <formula>LEFT(B1,2)="完了"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1048576 K1:L1048576 N1:O1048576">
-    <cfRule type="beginsWith" dxfId="4" priority="2" operator="beginsWith" text="〇">
+    <cfRule type="beginsWith" dxfId="6" priority="2" operator="beginsWith" text="〇">
       <formula>LEFT(H1,1)="〇"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="3" priority="1" operator="beginsWith" text="×">
+    <cfRule type="beginsWith" dxfId="5" priority="1" operator="beginsWith" text="×">
       <formula>LEFT(H1,1)="×"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3712,13 +3731,13 @@
   </sheetData>
   <phoneticPr fontId="4"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="beginsWith" dxfId="2" priority="1" operator="beginsWith" text="完了">
+    <cfRule type="beginsWith" dxfId="4" priority="1" operator="beginsWith" text="完了">
       <formula>LEFT(B1,2)="完了"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="1" priority="2" operator="beginsWith" text="エラー修正">
+    <cfRule type="beginsWith" dxfId="3" priority="2" operator="beginsWith" text="エラー修正">
       <formula>LEFT(B1,5)="エラー修正"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="0" priority="3" operator="beginsWith" text="着手">
+    <cfRule type="beginsWith" dxfId="2" priority="3" operator="beginsWith" text="着手">
       <formula>LEFT(B1,2)="着手"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/ディレクトリマップ_進捗表.xlsx
+++ b/ディレクトリマップ_進捗表.xlsx
@@ -553,7 +553,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="38">
+  <borders count="37">
     <border>
       <left/>
       <right/>
@@ -1021,19 +1021,6 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1317,28 +1304,14 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="14">
     <dxf>
       <fill>
         <patternFill>
@@ -1385,6 +1358,13 @@
       <fill>
         <patternFill>
           <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2711,30 +2691,30 @@
   </sheetData>
   <phoneticPr fontId="4"/>
   <conditionalFormatting sqref="A2">
-    <cfRule type="beginsWith" dxfId="14" priority="4" operator="beginsWith" text="完了">
+    <cfRule type="beginsWith" dxfId="13" priority="4" operator="beginsWith" text="完了">
       <formula>LEFT(A2,2)="完了"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="13" priority="5" operator="beginsWith" text="エラー修正">
+    <cfRule type="beginsWith" dxfId="12" priority="5" operator="beginsWith" text="エラー修正">
       <formula>LEFT(A2,5)="エラー修正"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="12" priority="6" operator="beginsWith" text="着手">
+    <cfRule type="beginsWith" dxfId="11" priority="6" operator="beginsWith" text="着手">
       <formula>LEFT(A2,2)="着手"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:I2 K2:L2 N2:O2">
-    <cfRule type="beginsWith" dxfId="11" priority="2" operator="beginsWith" text="×">
+    <cfRule type="beginsWith" dxfId="10" priority="2" operator="beginsWith" text="×">
       <formula>LEFT(H2,1)="×"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="10" priority="3" operator="beginsWith" text="〇">
+    <cfRule type="beginsWith" dxfId="9" priority="3" operator="beginsWith" text="〇">
       <formula>LEFT(H2,1)="〇"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:A45">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
       <formula>"着手"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3:K71 N3:N126 A4 A6:A23 A25:A26 A28 A30:A33">
       <formula1>$W$3:$W$6</formula1>
     </dataValidation>
@@ -3377,21 +3357,21 @@
   </sheetData>
   <phoneticPr fontId="4"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="beginsWith" dxfId="9" priority="5" operator="beginsWith" text="着手">
+    <cfRule type="beginsWith" dxfId="7" priority="5" operator="beginsWith" text="着手">
       <formula>LEFT(B1,2)="着手"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="8" priority="4" operator="beginsWith" text="エラー修正">
+    <cfRule type="beginsWith" dxfId="6" priority="4" operator="beginsWith" text="エラー修正">
       <formula>LEFT(B1,5)="エラー修正"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="7" priority="3" operator="beginsWith" text="完了">
+    <cfRule type="beginsWith" dxfId="5" priority="3" operator="beginsWith" text="完了">
       <formula>LEFT(B1,2)="完了"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1048576 K1:L1048576 N1:O1048576">
-    <cfRule type="beginsWith" dxfId="6" priority="2" operator="beginsWith" text="〇">
+    <cfRule type="beginsWith" dxfId="4" priority="2" operator="beginsWith" text="〇">
       <formula>LEFT(H1,1)="〇"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="5" priority="1" operator="beginsWith" text="×">
+    <cfRule type="beginsWith" dxfId="3" priority="1" operator="beginsWith" text="×">
       <formula>LEFT(H1,1)="×"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3731,13 +3711,13 @@
   </sheetData>
   <phoneticPr fontId="4"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="beginsWith" dxfId="4" priority="1" operator="beginsWith" text="完了">
+    <cfRule type="beginsWith" dxfId="2" priority="1" operator="beginsWith" text="完了">
       <formula>LEFT(B1,2)="完了"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="3" priority="2" operator="beginsWith" text="エラー修正">
+    <cfRule type="beginsWith" dxfId="1" priority="2" operator="beginsWith" text="エラー修正">
       <formula>LEFT(B1,5)="エラー修正"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="2" priority="3" operator="beginsWith" text="着手">
+    <cfRule type="beginsWith" dxfId="0" priority="3" operator="beginsWith" text="着手">
       <formula>LEFT(B1,2)="着手"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/ディレクトリマップ_進捗表.xlsx
+++ b/ディレクトリマップ_進捗表.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="120">
   <si>
     <t>ディレクトリマップ</t>
   </si>
@@ -426,6 +426,17 @@
     <t>URLバリデーションなど、補助機能</t>
     <rPh sb="13" eb="17">
       <t>ホジョキノウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ログイン/ログアウト</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ユーザー登録完了</t>
+    <rPh sb="6" eb="8">
+      <t>カンリョウ</t>
     </rPh>
     <phoneticPr fontId="4"/>
   </si>
@@ -2142,7 +2153,7 @@
         <v>27</v>
       </c>
       <c r="E16" s="88" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F16" s="16" t="s">
         <v>25</v>
@@ -2172,7 +2183,7 @@
         <v>29</v>
       </c>
       <c r="E17" s="45" t="s">
-        <v>28</v>
+        <v>118</v>
       </c>
       <c r="F17" s="16"/>
       <c r="G17" s="70"/>
@@ -2200,7 +2211,7 @@
         <v>24</v>
       </c>
       <c r="E18" s="45" t="s">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="F18" s="16" t="s">
         <v>31</v>

--- a/ディレクトリマップ_進捗表.xlsx
+++ b/ディレクトリマップ_進捗表.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="123">
   <si>
     <t>ディレクトリマップ</t>
   </si>
@@ -438,6 +438,18 @@
     <rPh sb="6" eb="8">
       <t>カンリョウ</t>
     </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>register.php</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>login_api.php、logout_api.php</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>register_api.php</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -2155,9 +2167,7 @@
       <c r="E16" s="88" t="s">
         <v>119</v>
       </c>
-      <c r="F16" s="16" t="s">
-        <v>25</v>
-      </c>
+      <c r="F16" s="16"/>
       <c r="G16" s="70"/>
       <c r="H16" s="70"/>
       <c r="I16" s="70"/>
@@ -2185,7 +2195,9 @@
       <c r="E17" s="45" t="s">
         <v>118</v>
       </c>
-      <c r="F17" s="16"/>
+      <c r="F17" s="16" t="s">
+        <v>121</v>
+      </c>
       <c r="G17" s="70"/>
       <c r="H17" s="70"/>
       <c r="I17" s="70"/>
@@ -2208,13 +2220,13 @@
       <c r="B18" s="68"/>
       <c r="C18" s="68"/>
       <c r="D18" s="70" t="s">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="E18" s="45" t="s">
         <v>110</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>31</v>
+        <v>122</v>
       </c>
       <c r="G18" s="70"/>
       <c r="H18" s="70"/>
@@ -2725,7 +2737,7 @@
       <formula>"着手"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3:K71 N3:N126 A4 A6:A23 A25:A26 A28 A30:A33">
       <formula1>$W$3:$W$6</formula1>
     </dataValidation>

--- a/ディレクトリマップ_進捗表.xlsx
+++ b/ディレクトリマップ_進捗表.xlsx
@@ -15,7 +15,7 @@
     <sheet name="ドロップダウンリスト" sheetId="5" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ディレクトリマップ!$A$1:$O$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ディレクトリマップ!$A$1:$O$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">ディレクトリマップold!$B$3:$B$22</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="126">
   <si>
     <t>ディレクトリマップ</t>
   </si>
@@ -450,6 +450,24 @@
   </si>
   <si>
     <t>register_api.php</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>config.php</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>各種設定など</t>
+    <rPh sb="0" eb="2">
+      <t>カクシュ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>utility</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -576,7 +594,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="37">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -1044,13 +1062,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1328,6 +1359,27 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1335,6 +1387,48 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="14">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1388,48 +1482,6 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1728,7 +1780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W37"/>
+  <dimension ref="A1:W39"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="7.88671875" style="61" customWidth="1"/>
@@ -1855,13 +1907,13 @@
     </row>
     <row r="5" spans="1:23">
       <c r="A5" s="76"/>
-      <c r="B5" s="84" t="s">
-        <v>87</v>
-      </c>
-      <c r="C5" s="81"/>
-      <c r="D5" s="82"/>
-      <c r="E5" s="76"/>
-      <c r="F5" s="76"/>
+      <c r="B5" s="93" t="s">
+        <v>125</v>
+      </c>
+      <c r="C5" s="97"/>
+      <c r="D5" s="98"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="99"/>
       <c r="G5" s="76"/>
       <c r="H5" s="76"/>
       <c r="I5" s="76"/>
@@ -1872,94 +1924,80 @@
       <c r="N5" s="76"/>
       <c r="O5" s="76"/>
       <c r="P5" s="62"/>
-      <c r="W5" s="28" t="s">
-        <v>23</v>
-      </c>
+      <c r="W5" s="28"/>
     </row>
     <row r="6" spans="1:23">
       <c r="A6" s="70" t="s">
         <v>115</v>
       </c>
-      <c r="B6" s="83"/>
-      <c r="C6" s="87" t="s">
-        <v>107</v>
-      </c>
-      <c r="D6" s="85"/>
-      <c r="E6" s="86"/>
-      <c r="F6" s="86"/>
-      <c r="G6" s="86"/>
-      <c r="H6" s="86"/>
-      <c r="I6" s="86"/>
-      <c r="J6" s="86"/>
-      <c r="K6" s="86"/>
-      <c r="L6" s="86"/>
-      <c r="M6" s="86"/>
-      <c r="N6" s="86"/>
-      <c r="O6" s="86"/>
+      <c r="B6" s="95" t="s">
+        <v>123</v>
+      </c>
+      <c r="C6" s="96"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="75" t="s">
+        <v>124</v>
+      </c>
+      <c r="F6" s="16"/>
+      <c r="G6" s="70"/>
+      <c r="H6" s="70"/>
+      <c r="I6" s="70"/>
+      <c r="J6" s="70"/>
+      <c r="K6" s="70"/>
+      <c r="L6" s="70"/>
+      <c r="M6" s="70"/>
+      <c r="N6" s="70"/>
+      <c r="O6" s="70"/>
       <c r="P6" s="62"/>
-      <c r="W6" s="28" t="s">
-        <v>26</v>
-      </c>
+      <c r="W6" s="28"/>
     </row>
     <row r="7" spans="1:23">
-      <c r="A7" s="70" t="s">
-        <v>115</v>
-      </c>
-      <c r="B7" s="68"/>
-      <c r="C7" s="68"/>
-      <c r="D7" s="70" t="s">
-        <v>88</v>
-      </c>
-      <c r="E7" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="G7" s="70"/>
-      <c r="H7" s="70"/>
-      <c r="I7" s="70"/>
-      <c r="J7" s="70"/>
-      <c r="K7" s="70" t="s">
-        <v>115</v>
-      </c>
-      <c r="L7" s="70"/>
-      <c r="M7" s="70"/>
-      <c r="N7" s="70" t="s">
-        <v>115</v>
-      </c>
-      <c r="O7" s="70"/>
+      <c r="A7" s="76"/>
+      <c r="B7" s="94" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="81"/>
+      <c r="D7" s="82"/>
+      <c r="E7" s="76"/>
+      <c r="F7" s="76"/>
+      <c r="G7" s="76"/>
+      <c r="H7" s="76"/>
+      <c r="I7" s="76"/>
+      <c r="J7" s="76"/>
+      <c r="K7" s="76"/>
+      <c r="L7" s="76"/>
+      <c r="M7" s="76"/>
+      <c r="N7" s="76"/>
+      <c r="O7" s="76"/>
       <c r="P7" s="62"/>
+      <c r="W7" s="28" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="8" spans="1:23">
       <c r="A8" s="70" t="s">
         <v>115</v>
       </c>
-      <c r="B8" s="68"/>
-      <c r="C8" s="68"/>
-      <c r="D8" s="70" t="s">
-        <v>56</v>
-      </c>
-      <c r="E8" s="45" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="G8" s="70"/>
-      <c r="H8" s="70"/>
-      <c r="I8" s="70"/>
-      <c r="J8" s="70"/>
-      <c r="K8" s="70" t="s">
-        <v>115</v>
-      </c>
-      <c r="L8" s="70"/>
-      <c r="M8" s="70"/>
-      <c r="N8" s="70" t="s">
-        <v>115</v>
-      </c>
-      <c r="O8" s="70"/>
+      <c r="B8" s="83"/>
+      <c r="C8" s="87" t="s">
+        <v>107</v>
+      </c>
+      <c r="D8" s="85"/>
+      <c r="E8" s="86"/>
+      <c r="F8" s="86"/>
+      <c r="G8" s="86"/>
+      <c r="H8" s="86"/>
+      <c r="I8" s="86"/>
+      <c r="J8" s="86"/>
+      <c r="K8" s="86"/>
+      <c r="L8" s="86"/>
+      <c r="M8" s="86"/>
+      <c r="N8" s="86"/>
+      <c r="O8" s="86"/>
       <c r="P8" s="62"/>
+      <c r="W8" s="28" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="9" spans="1:23">
       <c r="A9" s="70" t="s">
@@ -1968,13 +2006,13 @@
       <c r="B9" s="68"/>
       <c r="C9" s="68"/>
       <c r="D9" s="70" t="s">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="E9" s="45" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G9" s="70"/>
       <c r="H9" s="70"/>
@@ -1996,15 +2034,15 @@
         <v>115</v>
       </c>
       <c r="B10" s="68"/>
-      <c r="C10" s="69"/>
-      <c r="D10" s="72" t="s">
-        <v>51</v>
-      </c>
-      <c r="E10" s="52" t="s">
-        <v>60</v>
+      <c r="C10" s="68"/>
+      <c r="D10" s="70" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" s="45" t="s">
+        <v>55</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G10" s="70"/>
       <c r="H10" s="70"/>
@@ -2026,21 +2064,29 @@
         <v>115</v>
       </c>
       <c r="B11" s="68"/>
-      <c r="C11" s="87" t="s">
-        <v>89</v>
-      </c>
-      <c r="D11" s="85"/>
-      <c r="E11" s="86"/>
-      <c r="F11" s="86"/>
-      <c r="G11" s="86"/>
-      <c r="H11" s="86"/>
-      <c r="I11" s="86"/>
-      <c r="J11" s="86"/>
-      <c r="K11" s="86"/>
-      <c r="L11" s="86"/>
-      <c r="M11" s="86"/>
-      <c r="N11" s="86"/>
-      <c r="O11" s="86"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="70" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="70"/>
+      <c r="K11" s="70" t="s">
+        <v>115</v>
+      </c>
+      <c r="L11" s="70"/>
+      <c r="M11" s="70"/>
+      <c r="N11" s="70" t="s">
+        <v>115</v>
+      </c>
+      <c r="O11" s="70"/>
       <c r="P11" s="62"/>
     </row>
     <row r="12" spans="1:23">
@@ -2048,15 +2094,15 @@
         <v>115</v>
       </c>
       <c r="B12" s="68"/>
-      <c r="C12" s="68"/>
-      <c r="D12" s="70" t="s">
-        <v>47</v>
-      </c>
-      <c r="E12" s="45" t="s">
-        <v>42</v>
+      <c r="C12" s="69"/>
+      <c r="D12" s="72" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="52" t="s">
+        <v>60</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="G12" s="70"/>
       <c r="H12" s="70"/>
@@ -2078,29 +2124,21 @@
         <v>115</v>
       </c>
       <c r="B13" s="68"/>
-      <c r="C13" s="68"/>
-      <c r="D13" s="70" t="s">
-        <v>41</v>
-      </c>
-      <c r="E13" s="45" t="s">
-        <v>45</v>
-      </c>
-      <c r="F13" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="G13" s="70"/>
-      <c r="H13" s="70"/>
-      <c r="I13" s="70"/>
-      <c r="J13" s="70"/>
-      <c r="K13" s="70" t="s">
-        <v>115</v>
-      </c>
-      <c r="L13" s="70"/>
-      <c r="M13" s="70"/>
-      <c r="N13" s="70" t="s">
-        <v>115</v>
-      </c>
-      <c r="O13" s="70"/>
+      <c r="C13" s="87" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13" s="85"/>
+      <c r="E13" s="86"/>
+      <c r="F13" s="86"/>
+      <c r="G13" s="86"/>
+      <c r="H13" s="86"/>
+      <c r="I13" s="86"/>
+      <c r="J13" s="86"/>
+      <c r="K13" s="86"/>
+      <c r="L13" s="86"/>
+      <c r="M13" s="86"/>
+      <c r="N13" s="86"/>
+      <c r="O13" s="86"/>
       <c r="P13" s="62"/>
     </row>
     <row r="14" spans="1:23">
@@ -2108,15 +2146,15 @@
         <v>115</v>
       </c>
       <c r="B14" s="68"/>
-      <c r="C14" s="69"/>
-      <c r="D14" s="72" t="s">
-        <v>44</v>
+      <c r="C14" s="68"/>
+      <c r="D14" s="70" t="s">
+        <v>47</v>
       </c>
       <c r="E14" s="45" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G14" s="70"/>
       <c r="H14" s="70"/>
@@ -2138,21 +2176,29 @@
         <v>115</v>
       </c>
       <c r="B15" s="68"/>
-      <c r="C15" s="89" t="s">
-        <v>90</v>
-      </c>
-      <c r="D15" s="85"/>
-      <c r="E15" s="86"/>
-      <c r="F15" s="86"/>
-      <c r="G15" s="86"/>
-      <c r="H15" s="86"/>
-      <c r="I15" s="86"/>
-      <c r="J15" s="86"/>
-      <c r="K15" s="86"/>
-      <c r="L15" s="86"/>
-      <c r="M15" s="86"/>
-      <c r="N15" s="86"/>
-      <c r="O15" s="86"/>
+      <c r="C15" s="68"/>
+      <c r="D15" s="70" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" s="45" t="s">
+        <v>45</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="G15" s="70"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="70"/>
+      <c r="K15" s="70" t="s">
+        <v>115</v>
+      </c>
+      <c r="L15" s="70"/>
+      <c r="M15" s="70"/>
+      <c r="N15" s="70" t="s">
+        <v>115</v>
+      </c>
+      <c r="O15" s="70"/>
       <c r="P15" s="62"/>
     </row>
     <row r="16" spans="1:23">
@@ -2160,14 +2206,16 @@
         <v>115</v>
       </c>
       <c r="B16" s="68"/>
-      <c r="C16" s="92"/>
-      <c r="D16" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="E16" s="88" t="s">
-        <v>119</v>
-      </c>
-      <c r="F16" s="16"/>
+      <c r="C16" s="69"/>
+      <c r="D16" s="72" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="G16" s="70"/>
       <c r="H16" s="70"/>
       <c r="I16" s="70"/>
@@ -2188,46 +2236,36 @@
         <v>115</v>
       </c>
       <c r="B17" s="68"/>
-      <c r="C17" s="68"/>
-      <c r="D17" s="70" t="s">
-        <v>29</v>
-      </c>
-      <c r="E17" s="45" t="s">
-        <v>118</v>
-      </c>
-      <c r="F17" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="G17" s="70"/>
-      <c r="H17" s="70"/>
-      <c r="I17" s="70"/>
-      <c r="J17" s="70"/>
-      <c r="K17" s="70" t="s">
-        <v>115</v>
-      </c>
-      <c r="L17" s="70"/>
-      <c r="M17" s="70"/>
-      <c r="N17" s="70" t="s">
-        <v>115</v>
-      </c>
-      <c r="O17" s="70"/>
+      <c r="C17" s="89" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="85"/>
+      <c r="E17" s="86"/>
+      <c r="F17" s="86"/>
+      <c r="G17" s="86"/>
+      <c r="H17" s="86"/>
+      <c r="I17" s="86"/>
+      <c r="J17" s="86"/>
+      <c r="K17" s="86"/>
+      <c r="L17" s="86"/>
+      <c r="M17" s="86"/>
+      <c r="N17" s="86"/>
+      <c r="O17" s="86"/>
       <c r="P17" s="62"/>
     </row>
     <row r="18" spans="1:16">
       <c r="A18" s="70" t="s">
-        <v>20</v>
+        <v>115</v>
       </c>
       <c r="B18" s="68"/>
-      <c r="C18" s="68"/>
+      <c r="C18" s="92"/>
       <c r="D18" s="70" t="s">
-        <v>120</v>
-      </c>
-      <c r="E18" s="45" t="s">
-        <v>110</v>
-      </c>
-      <c r="F18" s="16" t="s">
-        <v>122</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="E18" s="88" t="s">
+        <v>119</v>
+      </c>
+      <c r="F18" s="16"/>
       <c r="G18" s="70"/>
       <c r="H18" s="70"/>
       <c r="I18" s="70"/>
@@ -2248,15 +2286,15 @@
         <v>115</v>
       </c>
       <c r="B19" s="68"/>
-      <c r="C19" s="69"/>
+      <c r="C19" s="68"/>
       <c r="D19" s="70" t="s">
-        <v>111</v>
+        <v>29</v>
       </c>
       <c r="E19" s="45" t="s">
-        <v>33</v>
+        <v>118</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>34</v>
+        <v>121</v>
       </c>
       <c r="G19" s="70"/>
       <c r="H19" s="70"/>
@@ -2275,24 +2313,32 @@
     </row>
     <row r="20" spans="1:16">
       <c r="A20" s="70" t="s">
-        <v>115</v>
+        <v>20</v>
       </c>
       <c r="B20" s="68"/>
-      <c r="C20" s="90" t="s">
-        <v>91</v>
-      </c>
-      <c r="D20" s="91"/>
-      <c r="E20" s="86"/>
-      <c r="F20" s="86"/>
-      <c r="G20" s="86"/>
-      <c r="H20" s="86"/>
-      <c r="I20" s="86"/>
-      <c r="J20" s="86"/>
-      <c r="K20" s="86"/>
-      <c r="L20" s="86"/>
-      <c r="M20" s="86"/>
-      <c r="N20" s="86"/>
-      <c r="O20" s="86"/>
+      <c r="C20" s="68"/>
+      <c r="D20" s="70" t="s">
+        <v>120</v>
+      </c>
+      <c r="E20" s="45" t="s">
+        <v>110</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G20" s="70"/>
+      <c r="H20" s="70"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="70"/>
+      <c r="K20" s="70" t="s">
+        <v>115</v>
+      </c>
+      <c r="L20" s="70"/>
+      <c r="M20" s="70"/>
+      <c r="N20" s="70" t="s">
+        <v>115</v>
+      </c>
+      <c r="O20" s="70"/>
       <c r="P20" s="62"/>
     </row>
     <row r="21" spans="1:16">
@@ -2302,13 +2348,13 @@
       <c r="B21" s="68"/>
       <c r="C21" s="69"/>
       <c r="D21" s="70" t="s">
-        <v>36</v>
+        <v>111</v>
       </c>
       <c r="E21" s="45" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G21" s="70"/>
       <c r="H21" s="70"/>
@@ -2330,10 +2376,10 @@
         <v>115</v>
       </c>
       <c r="B22" s="68"/>
-      <c r="C22" s="87" t="s">
-        <v>92</v>
-      </c>
-      <c r="D22" s="85"/>
+      <c r="C22" s="90" t="s">
+        <v>91</v>
+      </c>
+      <c r="D22" s="91"/>
       <c r="E22" s="86"/>
       <c r="F22" s="86"/>
       <c r="G22" s="86"/>
@@ -2351,15 +2397,17 @@
       <c r="A23" s="70" t="s">
         <v>115</v>
       </c>
-      <c r="B23" s="69"/>
+      <c r="B23" s="68"/>
       <c r="C23" s="69"/>
       <c r="D23" s="70" t="s">
-        <v>93</v>
-      </c>
-      <c r="E23" s="70" t="s">
-        <v>112</v>
-      </c>
-      <c r="F23" s="70"/>
+        <v>36</v>
+      </c>
+      <c r="E23" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>38</v>
+      </c>
       <c r="G23" s="70"/>
       <c r="H23" s="70"/>
       <c r="I23" s="70"/>
@@ -2376,36 +2424,38 @@
       <c r="P23" s="62"/>
     </row>
     <row r="24" spans="1:16">
-      <c r="A24" s="76"/>
-      <c r="B24" s="84" t="s">
-        <v>95</v>
-      </c>
-      <c r="C24" s="78"/>
-      <c r="D24" s="79"/>
-      <c r="E24" s="76"/>
-      <c r="F24" s="76"/>
-      <c r="G24" s="76"/>
-      <c r="H24" s="76"/>
-      <c r="I24" s="76"/>
-      <c r="J24" s="76"/>
-      <c r="K24" s="76"/>
-      <c r="L24" s="76"/>
-      <c r="M24" s="76"/>
-      <c r="N24" s="76"/>
-      <c r="O24" s="76"/>
+      <c r="A24" s="70" t="s">
+        <v>115</v>
+      </c>
+      <c r="B24" s="68"/>
+      <c r="C24" s="87" t="s">
+        <v>92</v>
+      </c>
+      <c r="D24" s="85"/>
+      <c r="E24" s="86"/>
+      <c r="F24" s="86"/>
+      <c r="G24" s="86"/>
+      <c r="H24" s="86"/>
+      <c r="I24" s="86"/>
+      <c r="J24" s="86"/>
+      <c r="K24" s="86"/>
+      <c r="L24" s="86"/>
+      <c r="M24" s="86"/>
+      <c r="N24" s="86"/>
+      <c r="O24" s="86"/>
       <c r="P24" s="62"/>
     </row>
     <row r="25" spans="1:16">
       <c r="A25" s="70" t="s">
         <v>115</v>
       </c>
-      <c r="B25" s="83"/>
-      <c r="C25" s="66" t="s">
-        <v>96</v>
-      </c>
-      <c r="D25" s="67"/>
+      <c r="B25" s="69"/>
+      <c r="C25" s="69"/>
+      <c r="D25" s="70" t="s">
+        <v>93</v>
+      </c>
       <c r="E25" s="70" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F25" s="70"/>
       <c r="G25" s="70"/>
@@ -2424,64 +2474,64 @@
       <c r="P25" s="62"/>
     </row>
     <row r="26" spans="1:16">
-      <c r="A26" s="70" t="s">
-        <v>115</v>
-      </c>
-      <c r="B26" s="69"/>
-      <c r="C26" s="64" t="s">
-        <v>97</v>
-      </c>
-      <c r="D26" s="65"/>
-      <c r="E26" s="70" t="s">
-        <v>117</v>
-      </c>
-      <c r="F26" s="70"/>
-      <c r="G26" s="70"/>
-      <c r="H26" s="70"/>
-      <c r="I26" s="70"/>
-      <c r="J26" s="70"/>
-      <c r="K26" s="70" t="s">
-        <v>115</v>
-      </c>
-      <c r="L26" s="70"/>
-      <c r="M26" s="70"/>
-      <c r="N26" s="70" t="s">
-        <v>115</v>
-      </c>
-      <c r="O26" s="70"/>
+      <c r="A26" s="76"/>
+      <c r="B26" s="84" t="s">
+        <v>95</v>
+      </c>
+      <c r="C26" s="78"/>
+      <c r="D26" s="79"/>
+      <c r="E26" s="76"/>
+      <c r="F26" s="76"/>
+      <c r="G26" s="76"/>
+      <c r="H26" s="76"/>
+      <c r="I26" s="76"/>
+      <c r="J26" s="76"/>
+      <c r="K26" s="76"/>
+      <c r="L26" s="76"/>
+      <c r="M26" s="76"/>
+      <c r="N26" s="76"/>
+      <c r="O26" s="76"/>
       <c r="P26" s="62"/>
     </row>
     <row r="27" spans="1:16">
-      <c r="A27" s="76"/>
-      <c r="B27" s="84" t="s">
-        <v>98</v>
-      </c>
-      <c r="C27" s="78"/>
-      <c r="D27" s="79"/>
-      <c r="E27" s="76"/>
-      <c r="F27" s="76"/>
-      <c r="G27" s="76"/>
-      <c r="H27" s="76"/>
-      <c r="I27" s="76"/>
-      <c r="J27" s="76"/>
-      <c r="K27" s="76"/>
-      <c r="L27" s="76"/>
-      <c r="M27" s="76"/>
-      <c r="N27" s="76"/>
-      <c r="O27" s="76"/>
+      <c r="A27" s="70" t="s">
+        <v>115</v>
+      </c>
+      <c r="B27" s="83"/>
+      <c r="C27" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="D27" s="67"/>
+      <c r="E27" s="70" t="s">
+        <v>113</v>
+      </c>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="70"/>
+      <c r="K27" s="70" t="s">
+        <v>115</v>
+      </c>
+      <c r="L27" s="70"/>
+      <c r="M27" s="70"/>
+      <c r="N27" s="70" t="s">
+        <v>115</v>
+      </c>
+      <c r="O27" s="70"/>
       <c r="P27" s="62"/>
     </row>
     <row r="28" spans="1:16">
       <c r="A28" s="70" t="s">
         <v>115</v>
       </c>
-      <c r="B28" s="71"/>
-      <c r="C28" s="66" t="s">
-        <v>99</v>
-      </c>
-      <c r="D28" s="67"/>
+      <c r="B28" s="69"/>
+      <c r="C28" s="64" t="s">
+        <v>97</v>
+      </c>
+      <c r="D28" s="65"/>
       <c r="E28" s="70" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F28" s="70"/>
       <c r="G28" s="70"/>
@@ -2502,7 +2552,7 @@
     <row r="29" spans="1:16">
       <c r="A29" s="76"/>
       <c r="B29" s="84" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C29" s="78"/>
       <c r="D29" s="79"/>
@@ -2523,12 +2573,14 @@
       <c r="A30" s="70" t="s">
         <v>115</v>
       </c>
-      <c r="B30" s="83"/>
+      <c r="B30" s="71"/>
       <c r="C30" s="66" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D30" s="67"/>
-      <c r="E30" s="70"/>
+      <c r="E30" s="70" t="s">
+        <v>114</v>
+      </c>
       <c r="F30" s="70"/>
       <c r="G30" s="70"/>
       <c r="H30" s="70"/>
@@ -2546,38 +2598,32 @@
       <c r="P30" s="62"/>
     </row>
     <row r="31" spans="1:16">
-      <c r="A31" s="70" t="s">
-        <v>115</v>
-      </c>
-      <c r="B31" s="68"/>
-      <c r="C31" s="66" t="s">
-        <v>102</v>
-      </c>
-      <c r="D31" s="67"/>
-      <c r="E31" s="70"/>
-      <c r="F31" s="70"/>
-      <c r="G31" s="70"/>
-      <c r="H31" s="70"/>
-      <c r="I31" s="70"/>
-      <c r="J31" s="70"/>
-      <c r="K31" s="70" t="s">
-        <v>115</v>
-      </c>
-      <c r="L31" s="70"/>
-      <c r="M31" s="70"/>
-      <c r="N31" s="70" t="s">
-        <v>115</v>
-      </c>
-      <c r="O31" s="70"/>
+      <c r="A31" s="76"/>
+      <c r="B31" s="84" t="s">
+        <v>100</v>
+      </c>
+      <c r="C31" s="78"/>
+      <c r="D31" s="79"/>
+      <c r="E31" s="76"/>
+      <c r="F31" s="76"/>
+      <c r="G31" s="76"/>
+      <c r="H31" s="76"/>
+      <c r="I31" s="76"/>
+      <c r="J31" s="76"/>
+      <c r="K31" s="76"/>
+      <c r="L31" s="76"/>
+      <c r="M31" s="76"/>
+      <c r="N31" s="76"/>
+      <c r="O31" s="76"/>
       <c r="P31" s="62"/>
     </row>
     <row r="32" spans="1:16">
       <c r="A32" s="70" t="s">
         <v>115</v>
       </c>
-      <c r="B32" s="68"/>
+      <c r="B32" s="83"/>
       <c r="C32" s="66" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D32" s="67"/>
       <c r="E32" s="70"/>
@@ -2601,11 +2647,11 @@
       <c r="A33" s="70" t="s">
         <v>115</v>
       </c>
-      <c r="B33" s="69"/>
-      <c r="C33" s="64" t="s">
-        <v>104</v>
-      </c>
-      <c r="D33" s="65"/>
+      <c r="B33" s="68"/>
+      <c r="C33" s="66" t="s">
+        <v>102</v>
+      </c>
+      <c r="D33" s="67"/>
       <c r="E33" s="70"/>
       <c r="F33" s="70"/>
       <c r="G33" s="70"/>
@@ -2624,122 +2670,174 @@
       <c r="P33" s="62"/>
     </row>
     <row r="34" spans="1:16">
-      <c r="A34" s="76"/>
-      <c r="B34" s="84" t="s">
+      <c r="A34" s="70" t="s">
+        <v>115</v>
+      </c>
+      <c r="B34" s="68"/>
+      <c r="C34" s="66" t="s">
+        <v>103</v>
+      </c>
+      <c r="D34" s="67"/>
+      <c r="E34" s="70"/>
+      <c r="F34" s="70"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="70"/>
+      <c r="I34" s="70"/>
+      <c r="J34" s="70"/>
+      <c r="K34" s="70" t="s">
+        <v>115</v>
+      </c>
+      <c r="L34" s="70"/>
+      <c r="M34" s="70"/>
+      <c r="N34" s="70" t="s">
+        <v>115</v>
+      </c>
+      <c r="O34" s="70"/>
+      <c r="P34" s="62"/>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35" s="70" t="s">
+        <v>115</v>
+      </c>
+      <c r="B35" s="69"/>
+      <c r="C35" s="64" t="s">
+        <v>104</v>
+      </c>
+      <c r="D35" s="65"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
+      <c r="I35" s="70"/>
+      <c r="J35" s="70"/>
+      <c r="K35" s="70" t="s">
+        <v>115</v>
+      </c>
+      <c r="L35" s="70"/>
+      <c r="M35" s="70"/>
+      <c r="N35" s="70" t="s">
+        <v>115</v>
+      </c>
+      <c r="O35" s="70"/>
+      <c r="P35" s="62"/>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36" s="76"/>
+      <c r="B36" s="84" t="s">
         <v>105</v>
       </c>
-      <c r="C34" s="78"/>
-      <c r="D34" s="79"/>
-      <c r="E34" s="76"/>
-      <c r="F34" s="76"/>
-      <c r="G34" s="76"/>
-      <c r="H34" s="76"/>
-      <c r="I34" s="76"/>
-      <c r="J34" s="76"/>
-      <c r="K34" s="76"/>
-      <c r="L34" s="76"/>
-      <c r="M34" s="76"/>
-      <c r="N34" s="76"/>
-      <c r="O34" s="76"/>
-      <c r="P34" s="62"/>
-    </row>
-    <row r="35" spans="1:16">
-      <c r="A35" s="70"/>
-      <c r="B35" s="83"/>
-      <c r="C35" s="87" t="s">
-        <v>94</v>
-      </c>
-      <c r="D35" s="85"/>
-      <c r="E35" s="86"/>
-      <c r="F35" s="86"/>
-      <c r="G35" s="86"/>
-      <c r="H35" s="86"/>
-      <c r="I35" s="86"/>
-      <c r="J35" s="86"/>
-      <c r="K35" s="86"/>
-      <c r="L35" s="86"/>
-      <c r="M35" s="86"/>
-      <c r="N35" s="86"/>
-      <c r="O35" s="86"/>
-      <c r="P35" s="62"/>
-    </row>
-    <row r="36" spans="1:16">
-      <c r="A36" s="70"/>
-      <c r="B36" s="68"/>
-      <c r="C36" s="68"/>
-      <c r="D36" s="70" t="s">
-        <v>66</v>
-      </c>
-      <c r="E36" s="70"/>
-      <c r="F36" s="70"/>
-      <c r="G36" s="70"/>
-      <c r="H36" s="70"/>
-      <c r="I36" s="70"/>
-      <c r="J36" s="70"/>
-      <c r="K36" s="70" t="s">
-        <v>115</v>
-      </c>
-      <c r="L36" s="70"/>
-      <c r="M36" s="70"/>
-      <c r="N36" s="70" t="s">
-        <v>115</v>
-      </c>
-      <c r="O36" s="70"/>
+      <c r="C36" s="78"/>
+      <c r="D36" s="79"/>
+      <c r="E36" s="76"/>
+      <c r="F36" s="76"/>
+      <c r="G36" s="76"/>
+      <c r="H36" s="76"/>
+      <c r="I36" s="76"/>
+      <c r="J36" s="76"/>
+      <c r="K36" s="76"/>
+      <c r="L36" s="76"/>
+      <c r="M36" s="76"/>
+      <c r="N36" s="76"/>
+      <c r="O36" s="76"/>
       <c r="P36" s="62"/>
     </row>
     <row r="37" spans="1:16">
       <c r="A37" s="70"/>
-      <c r="B37" s="69"/>
-      <c r="C37" s="69"/>
-      <c r="D37" s="72" t="s">
+      <c r="B37" s="83"/>
+      <c r="C37" s="87" t="s">
+        <v>94</v>
+      </c>
+      <c r="D37" s="85"/>
+      <c r="E37" s="86"/>
+      <c r="F37" s="86"/>
+      <c r="G37" s="86"/>
+      <c r="H37" s="86"/>
+      <c r="I37" s="86"/>
+      <c r="J37" s="86"/>
+      <c r="K37" s="86"/>
+      <c r="L37" s="86"/>
+      <c r="M37" s="86"/>
+      <c r="N37" s="86"/>
+      <c r="O37" s="86"/>
+      <c r="P37" s="62"/>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38" s="70"/>
+      <c r="B38" s="68"/>
+      <c r="C38" s="68"/>
+      <c r="D38" s="70" t="s">
+        <v>66</v>
+      </c>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="70"/>
+      <c r="K38" s="70" t="s">
+        <v>115</v>
+      </c>
+      <c r="L38" s="70"/>
+      <c r="M38" s="70"/>
+      <c r="N38" s="70" t="s">
+        <v>115</v>
+      </c>
+      <c r="O38" s="70"/>
+      <c r="P38" s="62"/>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39" s="70"/>
+      <c r="B39" s="69"/>
+      <c r="C39" s="69"/>
+      <c r="D39" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="E37" s="70"/>
-      <c r="F37" s="70"/>
-      <c r="G37" s="70"/>
-      <c r="H37" s="70"/>
-      <c r="I37" s="70"/>
-      <c r="J37" s="70"/>
-      <c r="K37" s="70" t="s">
-        <v>115</v>
-      </c>
-      <c r="L37" s="70"/>
-      <c r="M37" s="70"/>
-      <c r="N37" s="70" t="s">
-        <v>115</v>
-      </c>
-      <c r="O37" s="70"/>
-      <c r="P37" s="62"/>
+      <c r="E39" s="70"/>
+      <c r="F39" s="70"/>
+      <c r="G39" s="70"/>
+      <c r="H39" s="70"/>
+      <c r="I39" s="70"/>
+      <c r="J39" s="70"/>
+      <c r="K39" s="70" t="s">
+        <v>115</v>
+      </c>
+      <c r="L39" s="70"/>
+      <c r="M39" s="70"/>
+      <c r="N39" s="70" t="s">
+        <v>115</v>
+      </c>
+      <c r="O39" s="70"/>
+      <c r="P39" s="62"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4"/>
   <conditionalFormatting sqref="A2">
-    <cfRule type="beginsWith" dxfId="13" priority="4" operator="beginsWith" text="完了">
+    <cfRule type="beginsWith" dxfId="5" priority="4" operator="beginsWith" text="完了">
       <formula>LEFT(A2,2)="完了"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="12" priority="5" operator="beginsWith" text="エラー修正">
+    <cfRule type="beginsWith" dxfId="4" priority="5" operator="beginsWith" text="エラー修正">
       <formula>LEFT(A2,5)="エラー修正"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="11" priority="6" operator="beginsWith" text="着手">
+    <cfRule type="beginsWith" dxfId="3" priority="6" operator="beginsWith" text="着手">
       <formula>LEFT(A2,2)="着手"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:I2 K2:L2 N2:O2">
-    <cfRule type="beginsWith" dxfId="10" priority="2" operator="beginsWith" text="×">
+    <cfRule type="beginsWith" dxfId="2" priority="2" operator="beginsWith" text="×">
       <formula>LEFT(H2,1)="×"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="9" priority="3" operator="beginsWith" text="〇">
+    <cfRule type="beginsWith" dxfId="1" priority="3" operator="beginsWith" text="〇">
       <formula>LEFT(H2,1)="〇"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:A45">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+  <conditionalFormatting sqref="A4:A47">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"着手"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3:K71 N3:N126 A4 A6:A23 A25:A26 A28 A30:A33">
-      <formula1>$W$3:$W$6</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3:K73 N3:N128 A4:A6 A8:A25 A27:A28 A30 A32:A35">
+      <formula1>$W$3:$W$8</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3380,21 +3478,21 @@
   </sheetData>
   <phoneticPr fontId="4"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="beginsWith" dxfId="7" priority="5" operator="beginsWith" text="着手">
+    <cfRule type="beginsWith" dxfId="13" priority="5" operator="beginsWith" text="着手">
       <formula>LEFT(B1,2)="着手"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="6" priority="4" operator="beginsWith" text="エラー修正">
+    <cfRule type="beginsWith" dxfId="12" priority="4" operator="beginsWith" text="エラー修正">
       <formula>LEFT(B1,5)="エラー修正"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="5" priority="3" operator="beginsWith" text="完了">
+    <cfRule type="beginsWith" dxfId="11" priority="3" operator="beginsWith" text="完了">
       <formula>LEFT(B1,2)="完了"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1048576 K1:L1048576 N1:O1048576">
-    <cfRule type="beginsWith" dxfId="4" priority="2" operator="beginsWith" text="〇">
+    <cfRule type="beginsWith" dxfId="10" priority="2" operator="beginsWith" text="〇">
       <formula>LEFT(H1,1)="〇"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="3" priority="1" operator="beginsWith" text="×">
+    <cfRule type="beginsWith" dxfId="9" priority="1" operator="beginsWith" text="×">
       <formula>LEFT(H1,1)="×"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3734,13 +3832,13 @@
   </sheetData>
   <phoneticPr fontId="4"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="beginsWith" dxfId="2" priority="1" operator="beginsWith" text="完了">
+    <cfRule type="beginsWith" dxfId="8" priority="1" operator="beginsWith" text="完了">
       <formula>LEFT(B1,2)="完了"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="1" priority="2" operator="beginsWith" text="エラー修正">
+    <cfRule type="beginsWith" dxfId="7" priority="2" operator="beginsWith" text="エラー修正">
       <formula>LEFT(B1,5)="エラー修正"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="0" priority="3" operator="beginsWith" text="着手">
+    <cfRule type="beginsWith" dxfId="6" priority="3" operator="beginsWith" text="着手">
       <formula>LEFT(B1,2)="着手"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/ディレクトリマップ_進捗表.xlsx
+++ b/ディレクトリマップ_進捗表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4507"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="1992" windowHeight="12336"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="1992" windowHeight="12336" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="ディレクトリマップ" sheetId="7" r:id="rId1"/>
@@ -13,6 +13,7 @@
     <sheet name="Sheet3" sheetId="3" state="hidden" r:id="rId4"/>
     <sheet name="Sheet1" sheetId="4" state="hidden" r:id="rId5"/>
     <sheet name="ドロップダウンリスト" sheetId="5" state="hidden" r:id="rId6"/>
+    <sheet name="Sheet2" sheetId="8" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ディレクトリマップ!$A$1:$O$39</definedName>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="136">
   <si>
     <t>ディレクトリマップ</t>
   </si>
@@ -470,12 +471,98 @@
     <t>utility</t>
     <phoneticPr fontId="4"/>
   </si>
+  <si>
+    <t>2台目PCでの手順</t>
+  </si>
+  <si>
+    <t>1. XAMPPのphpMyAdmin（または MySQL）で空のDBを作成</t>
+  </si>
+  <si>
+    <t>CREATE DATABASE linestrike_deck_manager CHARACTER SET utf8mb4 COLLATE utf8mb4_general_ci;</t>
+  </si>
+  <si>
+    <t>2. リポジトリをクローン</t>
+  </si>
+  <si>
+    <t>git clone &lt;リポジトリURL&gt;</t>
+  </si>
+  <si>
+    <t>3. hooksをインストール</t>
+  </si>
+  <si>
+    <t>bash scripts/setup_hooks.sh</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">4. 以降は </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9.9"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>git pull</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> するだけで自動的にDB構造が同期される</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>post-merge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> hook が </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.9"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>dump.sql</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> を自動インポートしてくれます</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>まとめ:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> テーブル構造やデータは自動同期されるので手動でコピーは不要です。空のデータベース（名前だけ）を1回作るだけでOKです。</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -524,6 +611,48 @@
       <name val="游ゴシック Medium"/>
       <family val="3"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9.9"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.9"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="12">
@@ -1081,7 +1210,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1380,6 +1509,30 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1387,48 +1540,6 @@
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="14">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1482,6 +1593,48 @@
       <fill>
         <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2812,26 +2965,26 @@
   </sheetData>
   <phoneticPr fontId="4"/>
   <conditionalFormatting sqref="A2">
-    <cfRule type="beginsWith" dxfId="5" priority="4" operator="beginsWith" text="完了">
+    <cfRule type="beginsWith" dxfId="13" priority="4" operator="beginsWith" text="完了">
       <formula>LEFT(A2,2)="完了"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="4" priority="5" operator="beginsWith" text="エラー修正">
+    <cfRule type="beginsWith" dxfId="12" priority="5" operator="beginsWith" text="エラー修正">
       <formula>LEFT(A2,5)="エラー修正"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="3" priority="6" operator="beginsWith" text="着手">
+    <cfRule type="beginsWith" dxfId="11" priority="6" operator="beginsWith" text="着手">
       <formula>LEFT(A2,2)="着手"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:I2 K2:L2 N2:O2">
-    <cfRule type="beginsWith" dxfId="2" priority="2" operator="beginsWith" text="×">
+    <cfRule type="beginsWith" dxfId="10" priority="2" operator="beginsWith" text="×">
       <formula>LEFT(H2,1)="×"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="1" priority="3" operator="beginsWith" text="〇">
+    <cfRule type="beginsWith" dxfId="9" priority="3" operator="beginsWith" text="〇">
       <formula>LEFT(H2,1)="〇"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:A47">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
       <formula>"着手"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3478,21 +3631,21 @@
   </sheetData>
   <phoneticPr fontId="4"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="beginsWith" dxfId="13" priority="5" operator="beginsWith" text="着手">
+    <cfRule type="beginsWith" dxfId="7" priority="5" operator="beginsWith" text="着手">
       <formula>LEFT(B1,2)="着手"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="12" priority="4" operator="beginsWith" text="エラー修正">
+    <cfRule type="beginsWith" dxfId="6" priority="4" operator="beginsWith" text="エラー修正">
       <formula>LEFT(B1,5)="エラー修正"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="11" priority="3" operator="beginsWith" text="完了">
+    <cfRule type="beginsWith" dxfId="5" priority="3" operator="beginsWith" text="完了">
       <formula>LEFT(B1,2)="完了"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1048576 K1:L1048576 N1:O1048576">
-    <cfRule type="beginsWith" dxfId="10" priority="2" operator="beginsWith" text="〇">
+    <cfRule type="beginsWith" dxfId="4" priority="2" operator="beginsWith" text="〇">
       <formula>LEFT(H1,1)="〇"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="9" priority="1" operator="beginsWith" text="×">
+    <cfRule type="beginsWith" dxfId="3" priority="1" operator="beginsWith" text="×">
       <formula>LEFT(H1,1)="×"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3832,13 +3985,13 @@
   </sheetData>
   <phoneticPr fontId="4"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="beginsWith" dxfId="8" priority="1" operator="beginsWith" text="完了">
+    <cfRule type="beginsWith" dxfId="2" priority="1" operator="beginsWith" text="完了">
       <formula>LEFT(B1,2)="完了"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="7" priority="2" operator="beginsWith" text="エラー修正">
+    <cfRule type="beginsWith" dxfId="1" priority="2" operator="beginsWith" text="エラー修正">
       <formula>LEFT(B1,5)="エラー修正"</formula>
     </cfRule>
-    <cfRule type="beginsWith" dxfId="6" priority="3" operator="beginsWith" text="着手">
+    <cfRule type="beginsWith" dxfId="0" priority="3" operator="beginsWith" text="着手">
       <formula>LEFT(B1,2)="着手"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3880,4 +4033,84 @@
   <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A15"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
+  <cols>
+    <col min="1" max="1" width="120" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="27">
+      <c r="A1" s="100" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="101"/>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="102" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="13.8">
+      <c r="A4" s="103" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="102" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="13.8">
+      <c r="A6" s="103" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="102" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="13.8">
+      <c r="A8" s="103" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="13.8">
+      <c r="A9" s="102" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="104"/>
+    </row>
+    <row r="11" spans="1:1" ht="13.8">
+      <c r="A11" s="105" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="106"/>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="106"/>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="106"/>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="107" t="s">
+        <v>135</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="7"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>